--- a/figures/single_datasets_more_models.xlsx
+++ b/figures/single_datasets_more_models.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8055"/>
+    <workbookView windowHeight="19160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="109">
   <si>
     <t>model</t>
   </si>
@@ -71,25 +71,97 @@
     <t>airline_test</t>
   </si>
   <si>
+    <t>7563305346.1448</t>
+  </si>
+  <si>
+    <t>13883164014639880192.0000</t>
+  </si>
+  <si>
+    <t>2776632802927978.0000</t>
+  </si>
+  <si>
     <t>ZeroShot</t>
   </si>
   <si>
     <t>GAT</t>
   </si>
   <si>
+    <t>1.4254413843154907</t>
+  </si>
+  <si>
+    <t>10.51178574562073</t>
+  </si>
+  <si>
+    <t>4246559524913152.0</t>
+  </si>
+  <si>
+    <t>2706472000000.0</t>
+  </si>
+  <si>
     <t>GIN</t>
   </si>
   <si>
+    <t>1.2518115043640137</t>
+  </si>
+  <si>
+    <t>10.733089590072634</t>
+  </si>
+  <si>
+    <t>14.386540412902832</t>
+  </si>
+  <si>
     <t>GraphTransformer</t>
   </si>
   <si>
+    <t>1.2851417064666748</t>
+  </si>
+  <si>
+    <t>10.577110671997074</t>
+  </si>
+  <si>
+    <t>15.663810729980469</t>
+  </si>
+  <si>
     <t>HeteroGraphConv</t>
   </si>
   <si>
-    <t>HeteroGraphRGCN</t>
-  </si>
-  <si>
-    <t>HeteroGraphHGT</t>
+    <t>1.47044175863266</t>
+  </si>
+  <si>
+    <t>7.059790301322939</t>
+  </si>
+  <si>
+    <t>2059426752102400.0</t>
+  </si>
+  <si>
+    <t>RGCN</t>
+  </si>
+  <si>
+    <t>1.572965681552887</t>
+  </si>
+  <si>
+    <t>342522657033421.1</t>
+  </si>
+  <si>
+    <t>2586013499129856.0</t>
+  </si>
+  <si>
+    <t>36920516000000.0</t>
+  </si>
+  <si>
+    <t>HGT</t>
+  </si>
+  <si>
+    <t>1.4833649396896362</t>
+  </si>
+  <si>
+    <t>7.580171942710883</t>
+  </si>
+  <si>
+    <t>851666647646208.0</t>
+  </si>
+  <si>
+    <t>6169693000000.0</t>
   </si>
   <si>
     <t>carcinogenesis_train</t>
@@ -101,6 +173,60 @@
     <t>carcinogenesis_test</t>
   </si>
   <si>
+    <t>1.170433521270752</t>
+  </si>
+  <si>
+    <t>1.5384539723396302</t>
+  </si>
+  <si>
+    <t>4.9997358322143555</t>
+  </si>
+  <si>
+    <t>1.1147803664207458</t>
+  </si>
+  <si>
+    <t>1.463034808635712</t>
+  </si>
+  <si>
+    <t>2.746975898742676</t>
+  </si>
+  <si>
+    <t>1.116127610206604</t>
+  </si>
+  <si>
+    <t>1.4775597751140594</t>
+  </si>
+  <si>
+    <t>2.70538330078125</t>
+  </si>
+  <si>
+    <t>1.0980793833732605</t>
+  </si>
+  <si>
+    <t>1.4577942371368409</t>
+  </si>
+  <si>
+    <t>2.782331943511963</t>
+  </si>
+  <si>
+    <t>1.1129888892173767</t>
+  </si>
+  <si>
+    <t>1.511394774913788</t>
+  </si>
+  <si>
+    <t>3.266144275665283</t>
+  </si>
+  <si>
+    <t>1.1136494874954224</t>
+  </si>
+  <si>
+    <t>1.4970274031162263</t>
+  </si>
+  <si>
+    <t>3.14941143989563</t>
+  </si>
+  <si>
     <t>credit_train</t>
   </si>
   <si>
@@ -110,6 +236,66 @@
     <t>credit_test</t>
   </si>
   <si>
+    <t>5318045500.8220</t>
+  </si>
+  <si>
+    <t>1.2183896899223328</t>
+  </si>
+  <si>
+    <t>9.912918615341187</t>
+  </si>
+  <si>
+    <t>15.492010116577148</t>
+  </si>
+  <si>
+    <t>1.253815770149231</t>
+  </si>
+  <si>
+    <t>7.558435559272767</t>
+  </si>
+  <si>
+    <t>17.725364685058594</t>
+  </si>
+  <si>
+    <t>1.2288267016410828</t>
+  </si>
+  <si>
+    <t>1620669911950952.2</t>
+  </si>
+  <si>
+    <t>4239159833133056.0</t>
+  </si>
+  <si>
+    <t>139387100000000.0</t>
+  </si>
+  <si>
+    <t>1.2317951321601868</t>
+  </si>
+  <si>
+    <t>8.147341918945314</t>
+  </si>
+  <si>
+    <t>15.70398998260498</t>
+  </si>
+  <si>
+    <t>1.2983839511871338</t>
+  </si>
+  <si>
+    <t>8.014787530899047</t>
+  </si>
+  <si>
+    <t>17.628604888916016</t>
+  </si>
+  <si>
+    <t>1.2400031089782715</t>
+  </si>
+  <si>
+    <t>8.183376789093026</t>
+  </si>
+  <si>
+    <t>17.35907554626465</t>
+  </si>
+  <si>
     <t>employee_train</t>
   </si>
   <si>
@@ -117,17 +303,69 @@
   </si>
   <si>
     <t>employee_test</t>
+  </si>
+  <si>
+    <t>1549904795.7013</t>
+  </si>
+  <si>
+    <t>1.1840068101882935</t>
+  </si>
+  <si>
+    <t>2.325346684455873</t>
+  </si>
+  <si>
+    <t>11.576062202453613</t>
+  </si>
+  <si>
+    <t>1.116683006286621</t>
+  </si>
+  <si>
+    <t>1.6296322584152232</t>
+  </si>
+  <si>
+    <t>2219960013160448.0</t>
+  </si>
+  <si>
+    <t>1078784000000.0</t>
+  </si>
+  <si>
+    <t>1.0921440124511719</t>
+  </si>
+  <si>
+    <t>1.555583328008652</t>
+  </si>
+  <si>
+    <t>494280003026944.0</t>
+  </si>
+  <si>
+    <t>1.10256028175354</t>
+  </si>
+  <si>
+    <t>1.7103920876979832</t>
+  </si>
+  <si>
+    <t>7.274898529052734</t>
+  </si>
+  <si>
+    <t>1.0853397250175476</t>
+  </si>
+  <si>
+    <t>1.6002540409564983</t>
+  </si>
+  <si>
+    <t>11.415066719055176</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -587,21 +825,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -732,12 +970,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1059,14 +1309,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J36"/>
-  <sheetFormatPr defaultColWidth="8.79646017699115" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.79807692307692" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="18.3893805309735" customWidth="1"/>
-    <col min="3" max="3" width="21.0442477876106" customWidth="1"/>
-    <col min="4" max="4" width="15.9380530973451" customWidth="1"/>
+    <col min="1" max="1" width="18.3846153846154" customWidth="1"/>
+    <col min="3" max="3" width="21.0480769230769" customWidth="1"/>
+    <col min="4" max="4" width="15.9423076923077" customWidth="1"/>
+    <col min="6" max="6" width="14.0192307692308" customWidth="1"/>
+    <col min="10" max="10" width="18.1442307692308" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:10">
+    <row r="1" ht="17" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1098,7 +1350,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:10">
+    <row r="2" ht="34" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1111,28 +1363,28 @@
       <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2">
-        <v>0.0345</v>
-      </c>
-      <c r="F2">
-        <v>43954478.7202</v>
-      </c>
-      <c r="G2">
-        <v>1.0174</v>
-      </c>
-      <c r="H2">
-        <v>1.1112</v>
-      </c>
-      <c r="I2">
-        <v>7.1412</v>
-      </c>
-      <c r="J2">
-        <v>1.0361</v>
-      </c>
-    </row>
-    <row r="3" ht="27" spans="1:10">
+      <c r="E2" s="2">
+        <v>1.2479</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1.3237</v>
+      </c>
+      <c r="H2" s="2">
+        <v>9.1361</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="34" spans="1:10">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
@@ -1143,28 +1395,28 @@
       <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3">
-        <v>0.0354</v>
-      </c>
-      <c r="F3">
-        <v>6481.3574</v>
-      </c>
-      <c r="G3">
-        <v>1.0175</v>
-      </c>
-      <c r="H3">
-        <v>1.1099</v>
-      </c>
-      <c r="I3">
-        <v>7.1462</v>
-      </c>
-      <c r="J3">
-        <v>1.0369</v>
-      </c>
-    </row>
-    <row r="4" ht="27" spans="1:10">
+      <c r="E3" s="2">
+        <v>1.5025</v>
+      </c>
+      <c r="F3" s="2">
+        <v>107523.5781</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1.2427</v>
+      </c>
+      <c r="H3" s="2">
+        <v>11.2362</v>
+      </c>
+      <c r="I3" s="2">
+        <v>18.0151</v>
+      </c>
+      <c r="J3" s="2">
+        <v>2.5395</v>
+      </c>
+    </row>
+    <row r="4" ht="34" spans="1:10">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>11</v>
@@ -1175,28 +1427,28 @@
       <c r="D4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E4">
-        <v>0.09636371</v>
-      </c>
-      <c r="F4">
-        <v>8129.723</v>
-      </c>
-      <c r="G4">
-        <v>1.04046130180358</v>
-      </c>
-      <c r="H4">
-        <v>1.59021656513214</v>
-      </c>
-      <c r="I4">
-        <v>7.51457643508911</v>
-      </c>
-      <c r="J4">
-        <v>1.123518</v>
-      </c>
-    </row>
-    <row r="5" ht="27" spans="1:10">
+      <c r="E4" s="2">
+        <v>1.5001436</v>
+      </c>
+      <c r="F4" s="2">
+        <v>117042.31</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" ht="34" spans="1:10">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
@@ -1207,28 +1459,28 @@
       <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5">
-        <v>0.03826916</v>
-      </c>
-      <c r="F5">
-        <v>6562.084</v>
-      </c>
-      <c r="G5">
-        <v>1.01716148853302</v>
-      </c>
-      <c r="H5">
-        <v>1.12338417172431</v>
-      </c>
-      <c r="I5">
-        <v>7.17301654815673</v>
-      </c>
-      <c r="J5">
-        <v>1.0422169</v>
-      </c>
-    </row>
-    <row r="6" ht="27" spans="1:10">
+      <c r="E5" s="2">
+        <v>1.445538</v>
+      </c>
+      <c r="F5" s="2">
+        <v>105590.53</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="2">
+        <v>2.4881754</v>
+      </c>
+    </row>
+    <row r="6" ht="34" spans="1:10">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>11</v>
@@ -1239,28 +1491,28 @@
       <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E6">
-        <v>0.035421286</v>
-      </c>
-      <c r="F6">
-        <v>6440.157</v>
-      </c>
-      <c r="G6">
-        <v>1.01644366979599</v>
-      </c>
-      <c r="H6">
-        <v>1.11716148853302</v>
-      </c>
-      <c r="I6">
-        <v>7.16953134536743</v>
-      </c>
-      <c r="J6">
-        <v>1.037142</v>
-      </c>
-    </row>
-    <row r="7" ht="27" spans="1:10">
+      <c r="E6" s="2">
+        <v>1.4395915</v>
+      </c>
+      <c r="F6" s="2">
+        <v>107088.77</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="2">
+        <v>2.488775</v>
+      </c>
+    </row>
+    <row r="7" ht="34" spans="1:10">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>11</v>
@@ -1271,28 +1523,28 @@
       <c r="D7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E7">
-        <v>0.015957432</v>
-      </c>
-      <c r="F7">
-        <v>2657.8823</v>
-      </c>
-      <c r="G7">
-        <v>1.01148235797882</v>
-      </c>
-      <c r="H7">
-        <v>1.04823076725006</v>
-      </c>
-      <c r="I7">
-        <v>1.15286004543304</v>
-      </c>
-      <c r="J7">
-        <v>1.016141</v>
-      </c>
-    </row>
-    <row r="8" ht="27" spans="1:10">
+      <c r="E7" s="2">
+        <v>1.8756002</v>
+      </c>
+      <c r="F7" s="2">
+        <v>66620.74</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="2">
+        <v>944581300000</v>
+      </c>
+    </row>
+    <row r="8" ht="34" spans="1:10">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -1303,28 +1555,28 @@
       <c r="D8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E8">
-        <v>0.02421118</v>
-      </c>
-      <c r="F8">
-        <v>5132.539</v>
-      </c>
-      <c r="G8">
-        <v>1.01755827665328</v>
-      </c>
-      <c r="H8">
-        <v>1.06696974635124</v>
-      </c>
-      <c r="I8">
-        <v>1.45922780036926</v>
-      </c>
-      <c r="J8">
-        <v>1.0253067</v>
-      </c>
-    </row>
-    <row r="9" ht="27" spans="1:10">
+      <c r="E8" s="2">
+        <v>2.412917</v>
+      </c>
+      <c r="F8" s="2">
+        <v>71496.04</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="34" spans="1:10">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>11</v>
@@ -1335,23 +1587,23 @@
       <c r="D9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E9">
-        <v>0.01760273</v>
-      </c>
-      <c r="F9">
-        <v>3231.8914</v>
-      </c>
-      <c r="G9">
-        <v>1.0123142004013</v>
-      </c>
-      <c r="H9">
-        <v>1.051118683815</v>
-      </c>
-      <c r="I9">
-        <v>1.23572027683258</v>
-      </c>
-      <c r="J9">
-        <v>1.0179305</v>
+      <c r="E9" s="2">
+        <v>2.3766425</v>
+      </c>
+      <c r="F9" s="2">
+        <v>84593.836</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="2:4">
@@ -1359,780 +1611,780 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" ht="40.5" spans="1:10">
+    <row r="11" ht="51" spans="1:10">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.1752</v>
+      </c>
+      <c r="F11" s="2">
+        <v>547946116.2162</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1.1351</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1.533</v>
+      </c>
+      <c r="I11" s="2">
+        <v>3.8088</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1.1899</v>
+      </c>
+    </row>
+    <row r="12" ht="51" spans="1:10">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.1401</v>
+      </c>
+      <c r="F12" s="2">
+        <v>5909.6982</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1.1056</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1.4214</v>
+      </c>
+      <c r="I12" s="2">
+        <v>2.4232</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1.1472</v>
+      </c>
+    </row>
+    <row r="13" ht="51" spans="1:10">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.19285122</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8330.644</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1.2190052</v>
+      </c>
+    </row>
+    <row r="14" ht="51" spans="1:10">
+      <c r="A14" t="s">
         <v>23</v>
       </c>
-      <c r="E11">
-        <v>0.1455</v>
-      </c>
-      <c r="F11">
-        <v>28344697.366</v>
-      </c>
-      <c r="G11">
-        <v>1.1196</v>
-      </c>
-      <c r="H11">
-        <v>1.4746</v>
-      </c>
-      <c r="I11">
-        <v>1.9879</v>
-      </c>
-      <c r="J11">
-        <v>1.1592</v>
-      </c>
-    </row>
-    <row r="12" ht="40.5" spans="1:10">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12">
-        <v>0.021</v>
-      </c>
-      <c r="F12">
-        <v>577.5229</v>
-      </c>
-      <c r="G12">
-        <v>1.0115</v>
-      </c>
-      <c r="H12">
-        <v>1.0826</v>
-      </c>
-      <c r="I12">
-        <v>1.2799</v>
-      </c>
-      <c r="J12">
-        <v>1.0215</v>
-      </c>
-    </row>
-    <row r="13" ht="40.5" spans="1:10">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13">
-        <v>0.090392165</v>
-      </c>
-      <c r="F13">
-        <v>2421.757</v>
-      </c>
-      <c r="G13">
-        <v>1.06446301937103</v>
-      </c>
-      <c r="H13">
-        <v>1.27067001461982</v>
-      </c>
-      <c r="I13">
-        <v>1.79010903835296</v>
-      </c>
-      <c r="J13">
-        <v>1.0934775</v>
-      </c>
-    </row>
-    <row r="14" ht="40.5" spans="1:10">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
       <c r="B14" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14">
-        <v>0.031235248</v>
-      </c>
-      <c r="F14">
-        <v>856.50055</v>
-      </c>
-      <c r="G14">
-        <v>1.01594650745391</v>
-      </c>
-      <c r="H14">
-        <v>1.11731915473938</v>
-      </c>
-      <c r="I14">
-        <v>1.36087822914123</v>
-      </c>
-      <c r="J14">
-        <v>1.0322074</v>
-      </c>
-    </row>
-    <row r="15" ht="40.5" spans="1:10">
+        <v>47</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.14981426</v>
+      </c>
+      <c r="F14" s="2">
+        <v>6537.7275</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1.1639385</v>
+      </c>
+    </row>
+    <row r="15" ht="51" spans="1:10">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15">
-        <v>0.037939556</v>
-      </c>
-      <c r="F15">
-        <v>974.2079</v>
-      </c>
-      <c r="G15">
-        <v>1.02334916591644</v>
-      </c>
-      <c r="H15">
-        <v>1.12860708236694</v>
-      </c>
-      <c r="I15">
-        <v>1.74721574783325</v>
-      </c>
-      <c r="J15">
-        <v>1.0394349</v>
-      </c>
-    </row>
-    <row r="16" ht="40.5" spans="1:10">
+        <v>47</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.15142576</v>
+      </c>
+      <c r="F15" s="2">
+        <v>6287.6636</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1.1637248</v>
+      </c>
+    </row>
+    <row r="16" ht="51" spans="1:10">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16">
-        <v>0.027713202</v>
-      </c>
-      <c r="F16">
-        <v>751.71594</v>
-      </c>
-      <c r="G16">
-        <v>1.01351541280746</v>
-      </c>
-      <c r="H16">
-        <v>1.11396461129188</v>
-      </c>
-      <c r="I16">
-        <v>1.27188098430633</v>
-      </c>
-      <c r="J16">
-        <v>1.0286384</v>
-      </c>
-    </row>
-    <row r="17" ht="40.5" spans="1:10">
+        <v>47</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.13606316</v>
+      </c>
+      <c r="F16" s="2">
+        <v>5900.6396</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1.1474996</v>
+      </c>
+    </row>
+    <row r="17" ht="51" spans="1:10">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17">
-        <v>0.060880285</v>
-      </c>
-      <c r="F17">
-        <v>1630.7145</v>
-      </c>
-      <c r="G17">
-        <v>1.04328221082687</v>
-      </c>
-      <c r="H17">
-        <v>1.18196131587028</v>
-      </c>
-      <c r="I17">
-        <v>1.55796372890472</v>
-      </c>
-      <c r="J17">
-        <v>1.064078</v>
-      </c>
-    </row>
-    <row r="18" ht="40.5" spans="1:10">
+        <v>47</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.1537943</v>
+      </c>
+      <c r="F17" s="2">
+        <v>6937.3037</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1.1691586</v>
+      </c>
+    </row>
+    <row r="18" ht="51" spans="1:10">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18">
-        <v>0.02686338</v>
-      </c>
-      <c r="F18">
-        <v>734.7291</v>
-      </c>
-      <c r="G18">
-        <v>1.01263546943664</v>
-      </c>
-      <c r="H18">
-        <v>1.11357686519622</v>
-      </c>
-      <c r="I18">
-        <v>1.27368330955505</v>
-      </c>
-      <c r="J18">
-        <v>1.0277246</v>
+        <v>47</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.14001831</v>
+      </c>
+      <c r="F18" s="2">
+        <v>6898.1963</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1.1645327</v>
       </c>
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" ht="27" spans="1:10">
+    <row r="20" ht="34" spans="1:10">
       <c r="A20" t="s">
         <v>10</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20">
-        <v>0.123</v>
-      </c>
-      <c r="F20">
-        <v>1165683210.1617</v>
-      </c>
-      <c r="G20">
-        <v>1.0465</v>
-      </c>
-      <c r="H20">
-        <v>1.244</v>
-      </c>
-      <c r="I20">
-        <v>9.0694</v>
-      </c>
-      <c r="J20">
-        <v>1.1297</v>
-      </c>
-    </row>
-    <row r="21" ht="27" spans="1:10">
+        <v>68</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.9675</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1.6113</v>
+      </c>
+      <c r="H20" s="2">
+        <v>5.5335</v>
+      </c>
+      <c r="I20" s="2">
+        <v>9.8392</v>
+      </c>
+      <c r="J20" s="2">
+        <v>2.1359</v>
+      </c>
+    </row>
+    <row r="21" ht="34" spans="1:10">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21">
-        <v>0.0715</v>
-      </c>
-      <c r="F21">
-        <v>8485.4912</v>
-      </c>
-      <c r="G21">
-        <v>1.0271</v>
-      </c>
-      <c r="H21">
-        <v>1.1258</v>
-      </c>
-      <c r="I21">
-        <v>9.3152</v>
-      </c>
-      <c r="J21">
-        <v>1.0757</v>
-      </c>
-    </row>
-    <row r="22" ht="27" spans="1:10">
+        <v>68</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.605</v>
+      </c>
+      <c r="F21" s="2">
+        <v>78244.5312</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1.1756</v>
+      </c>
+      <c r="H21" s="2">
+        <v>8.5086</v>
+      </c>
+      <c r="I21" s="2">
+        <v>15.5959</v>
+      </c>
+      <c r="J21" s="2">
+        <v>2.1432</v>
+      </c>
+    </row>
+    <row r="22" ht="34" spans="1:10">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22">
-        <v>0.7248707</v>
-      </c>
-      <c r="F22">
-        <v>30008.668</v>
-      </c>
-      <c r="G22">
-        <v>1.15473157167434</v>
-      </c>
-      <c r="H22">
-        <v>4.77641685009002</v>
-      </c>
-      <c r="I22">
-        <v>9.67427730560302</v>
-      </c>
-      <c r="J22">
-        <v>1.7512348</v>
-      </c>
-    </row>
-    <row r="23" ht="27" spans="1:10">
+        <v>68</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.34481657</v>
+      </c>
+      <c r="F22" s="2">
+        <v>105311.71</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="2">
+        <v>2.9237933</v>
+      </c>
+    </row>
+    <row r="23" ht="34" spans="1:10">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23">
-        <v>0.077822305</v>
-      </c>
-      <c r="F23">
-        <v>6675.049</v>
-      </c>
-      <c r="G23">
-        <v>1.02468305826187</v>
-      </c>
-      <c r="H23">
-        <v>1.24203224778175</v>
-      </c>
-      <c r="I23">
-        <v>213919989760000</v>
-      </c>
-      <c r="J23">
-        <v>184160000000</v>
-      </c>
-    </row>
-    <row r="24" ht="27" spans="1:10">
+        <v>68</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.5355272</v>
+      </c>
+      <c r="F23" s="2">
+        <v>81561.51</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J23" s="2">
+        <v>2.1719232</v>
+      </c>
+    </row>
+    <row r="24" ht="34" spans="1:10">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24">
-        <v>0.15251987</v>
-      </c>
-      <c r="F24">
-        <v>9559.356</v>
-      </c>
-      <c r="G24">
-        <v>1.05470651388168</v>
-      </c>
-      <c r="H24">
-        <v>1.8637247622013</v>
-      </c>
-      <c r="I24">
-        <v>198559995527168</v>
-      </c>
-      <c r="J24">
-        <v>209520000000</v>
-      </c>
-    </row>
-    <row r="25" ht="27" spans="1:10">
+        <v>68</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0.6456271</v>
+      </c>
+      <c r="F24" s="2">
+        <v>267938</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" ht="34" spans="1:10">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25">
-        <v>0.041965913</v>
-      </c>
-      <c r="F25">
-        <v>5784.315</v>
-      </c>
-      <c r="G25">
-        <v>1.02011549472808</v>
-      </c>
-      <c r="H25">
-        <v>1.11731639504432</v>
-      </c>
-      <c r="I25">
-        <v>10.9713163375854</v>
-      </c>
-      <c r="J25">
-        <v>1.0479103</v>
-      </c>
-    </row>
-    <row r="26" ht="27" spans="1:10">
+        <v>68</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0.35211045</v>
+      </c>
+      <c r="F25" s="2">
+        <v>98159.79</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="J25" s="2">
+        <v>2.4232278</v>
+      </c>
+    </row>
+    <row r="26" ht="34" spans="1:10">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26">
-        <v>0.15563254</v>
-      </c>
-      <c r="F26">
-        <v>13981.024</v>
-      </c>
-      <c r="G26">
-        <v>1.09377044439315</v>
-      </c>
-      <c r="H26">
-        <v>1.45710324048995</v>
-      </c>
-      <c r="I26">
-        <v>10.9371423721313</v>
-      </c>
-      <c r="J26">
-        <v>1.1988226</v>
-      </c>
-    </row>
-    <row r="27" ht="27" spans="1:10">
+        <v>68</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.37838343</v>
+      </c>
+      <c r="F26" s="2">
+        <v>101029.92</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J26" s="2">
+        <v>2.5478165</v>
+      </c>
+    </row>
+    <row r="27" ht="34" spans="1:10">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27">
-        <v>0.10824648</v>
-      </c>
-      <c r="F27">
-        <v>10156.411</v>
-      </c>
-      <c r="G27">
-        <v>1.03178775310516</v>
-      </c>
-      <c r="H27">
-        <v>1.16832135915756</v>
-      </c>
-      <c r="I27">
-        <v>8.98857307434082</v>
-      </c>
-      <c r="J27">
-        <v>1.1147262</v>
+        <v>68</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.46706817</v>
+      </c>
+      <c r="F27" s="2">
+        <v>83133.64</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="J27" s="2">
+        <v>2.2263298</v>
       </c>
     </row>
     <row r="28" spans="2:4">
       <c r="B28" s="1"/>
       <c r="D28" s="1"/>
     </row>
-    <row r="29" ht="27" spans="1:10">
+    <row r="29" ht="34" spans="1:10">
       <c r="A29" t="s">
         <v>10</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.1594</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1.0873</v>
+      </c>
+      <c r="H29" s="2">
+        <v>1.5859</v>
+      </c>
+      <c r="I29" s="2">
+        <v>6.6097</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1.1738</v>
+      </c>
+    </row>
+    <row r="30" ht="34" spans="1:10">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.4078</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1180437.25</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1.101</v>
+      </c>
+      <c r="H30" s="2">
+        <v>1.9773</v>
+      </c>
+      <c r="I30" s="2">
+        <v>348.019</v>
+      </c>
+      <c r="J30" s="2">
+        <v>1.4394</v>
+      </c>
+    </row>
+    <row r="31" ht="34" spans="1:10">
+      <c r="A31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.23356697</v>
+      </c>
+      <c r="F31" s="2">
+        <v>34237.887</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J31" s="2">
+        <v>1.3385154</v>
+      </c>
+    </row>
+    <row r="32" ht="34" spans="1:10">
+      <c r="A32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.22348526</v>
+      </c>
+      <c r="F32" s="2">
+        <v>27240.627</v>
+      </c>
+      <c r="G32" s="2">
+        <v>1.0967873930931</v>
+      </c>
+      <c r="H32" s="2">
+        <v>1.62541663050651</v>
+      </c>
+      <c r="I32" s="2">
+        <v>8.33373069763183</v>
+      </c>
+      <c r="J32" s="2">
+        <v>1.239719</v>
+      </c>
+    </row>
+    <row r="33" ht="34" spans="1:10">
+      <c r="A33" t="s">
         <v>27</v>
       </c>
-      <c r="C29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E29">
-        <v>0.1787</v>
-      </c>
-      <c r="F29">
-        <v>1371704950.4605</v>
-      </c>
-      <c r="G29">
-        <v>1.0979</v>
-      </c>
-      <c r="H29">
-        <v>1.7198</v>
-      </c>
-      <c r="I29">
-        <v>4.0519</v>
-      </c>
-      <c r="J29">
-        <v>1.2008</v>
-      </c>
-    </row>
-    <row r="30" ht="27" spans="1:10">
-      <c r="A30" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30">
-        <v>0.1719</v>
-      </c>
-      <c r="F30">
-        <v>19277.9395</v>
-      </c>
-      <c r="G30">
-        <v>1.1031</v>
-      </c>
-      <c r="H30">
-        <v>1.7079</v>
-      </c>
-      <c r="I30">
-        <v>3.4426</v>
-      </c>
-      <c r="J30">
-        <v>1.1947</v>
-      </c>
-    </row>
-    <row r="31" ht="27" spans="1:10">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E31">
-        <v>0.29316333</v>
-      </c>
-      <c r="F31">
-        <v>26372.426</v>
-      </c>
-      <c r="G31">
-        <v>1.1365458369255</v>
-      </c>
-      <c r="H31">
-        <v>2.16591197252273</v>
-      </c>
-      <c r="I31">
-        <v>2.16591197252273</v>
-      </c>
-      <c r="J31">
-        <v>2.16591197252273</v>
-      </c>
-    </row>
-    <row r="32" ht="27" spans="1:10">
-      <c r="A32" t="s">
-        <v>16</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32">
-        <v>0.1629563</v>
-      </c>
-      <c r="F32">
-        <v>19668.309</v>
-      </c>
-      <c r="G32">
-        <v>1.10412645339965</v>
-      </c>
-      <c r="H32">
-        <v>1.62694846391677</v>
-      </c>
-      <c r="I32">
-        <v>4.0827612876892</v>
-      </c>
-      <c r="J32">
-        <v>1.1955043</v>
-      </c>
-    </row>
-    <row r="33" ht="27" spans="1:10">
-      <c r="A33" t="s">
-        <v>17</v>
-      </c>
       <c r="B33" s="1" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33">
-        <v>0.16040616</v>
-      </c>
-      <c r="F33">
-        <v>18275.129</v>
-      </c>
-      <c r="G33">
-        <v>1.10439503192901</v>
-      </c>
-      <c r="H33">
-        <v>1.65478922724723</v>
-      </c>
-      <c r="I33">
-        <v>3.35362219810485</v>
-      </c>
-      <c r="J33">
-        <v>1.1900938</v>
-      </c>
-    </row>
-    <row r="34" ht="27" spans="1:10">
+        <v>91</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.18217385</v>
+      </c>
+      <c r="F33" s="2">
+        <v>29404.387</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" ht="34" spans="1:10">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E34">
-        <v>0.15472482</v>
-      </c>
-      <c r="F34">
-        <v>19577.523</v>
-      </c>
-      <c r="G34">
-        <v>1.10097068548202</v>
-      </c>
-      <c r="H34">
-        <v>1.62992405295372</v>
-      </c>
-      <c r="I34">
-        <v>3.86833572387695</v>
-      </c>
-      <c r="J34">
-        <v>1.1995535</v>
-      </c>
-    </row>
-    <row r="35" ht="27" spans="1:10">
+        <v>91</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.14692654</v>
+      </c>
+      <c r="F34" s="2">
+        <v>21423.318</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J34" s="2">
+        <v>98856000000</v>
+      </c>
+    </row>
+    <row r="35" ht="34" spans="1:10">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35">
-        <v>0.21453814</v>
-      </c>
-      <c r="F35">
-        <v>20119.021</v>
-      </c>
-      <c r="G35">
-        <v>1.14019948244094</v>
-      </c>
-      <c r="H35">
-        <v>1.79349338412284</v>
-      </c>
-      <c r="I35">
-        <v>5.96395826339721</v>
-      </c>
-      <c r="J35">
-        <v>1.2467557</v>
-      </c>
-    </row>
-    <row r="36" ht="27" spans="1:10">
+        <v>91</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.19926827</v>
+      </c>
+      <c r="F35" s="2">
+        <v>27078.643</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J35" s="2">
+        <v>1.2238714</v>
+      </c>
+    </row>
+    <row r="36" ht="34" spans="1:10">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36">
-        <v>0.1716283</v>
-      </c>
-      <c r="F36">
-        <v>18535.531</v>
-      </c>
-      <c r="G36">
-        <v>1.10518956184387</v>
-      </c>
-      <c r="H36">
-        <v>1.75390605330467</v>
-      </c>
-      <c r="I36">
-        <v>118639999057920</v>
-      </c>
-      <c r="J36">
-        <v>23727999000</v>
+        <v>91</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.15197814</v>
+      </c>
+      <c r="F36" s="2">
+        <v>23212.441</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="J36" s="2">
+        <v>1.1759076</v>
       </c>
     </row>
   </sheetData>
